--- a/tools/보정계산서.xlsx
+++ b/tools/보정계산서.xlsx
@@ -8381,7 +8381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T79"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8404,6 +8404,8 @@
     <col width="11" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8434,7 +8436,7 @@
         </is>
       </c>
       <c r="C4" s="7">
-        <f>IF(SUMPRODUCT(--($Q$6:$Q$79="★동점"))=0,"0건 (정상)",SUMPRODUCT(--($Q$6:$Q$79="★동점"))&amp;"건 ★ 개정 2 위반 — 순위가 중복되어 산식이 깨진다. 원점수를 고쳐라")</f>
+        <f>IF(COUNTIF($Q$6:$Q$79,"★동점")=0,"0건 (정상)",COUNTIF($Q$6:$Q$79,"★동점")&amp;"건 ★ 개정 2 위반 — 순위가 중복되어 산식이 깨진다. 원점수를 고쳐라")</f>
         <v/>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -8553,6 +8555,18 @@
           <t>키 (계산용)</t>
         </is>
       </c>
+      <c r="U5" s="10" t="inlineStr">
+        <is>
+          <t>절단 전 보정점수
+(60·100 미적용)</t>
+        </is>
+      </c>
+      <c r="V5" s="10" t="inlineStr">
+        <is>
+          <t>절단 전 조정 후 점수
+(60·100 미적용)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
@@ -8639,6 +8653,14 @@
         <f>$E6&amp;"|"&amp;$C6</f>
         <v/>
       </c>
+      <c r="U6" s="24">
+        <f>IF($G6&lt;6,"",80+7*$K6/$I6)</f>
+        <v/>
+      </c>
+      <c r="V6" s="24">
+        <f>IF($N6="",$M6,$M6+$N6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
@@ -8725,6 +8747,14 @@
         <f>$E7&amp;"|"&amp;$C7</f>
         <v/>
       </c>
+      <c r="U7" s="24">
+        <f>IF($G7&lt;6,"",80+7*$K7/$I7)</f>
+        <v/>
+      </c>
+      <c r="V7" s="24">
+        <f>IF($N7="",$M7,$M7+$N7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
@@ -8811,6 +8841,14 @@
         <f>$E8&amp;"|"&amp;$C8</f>
         <v/>
       </c>
+      <c r="U8" s="24">
+        <f>IF($G8&lt;6,"",80+7*$K8/$I8)</f>
+        <v/>
+      </c>
+      <c r="V8" s="24">
+        <f>IF($N8="",$M8,$M8+$N8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -8895,6 +8933,14 @@
       </c>
       <c r="T9" s="20">
         <f>$E9&amp;"|"&amp;$C9</f>
+        <v/>
+      </c>
+      <c r="U9" s="24">
+        <f>IF($G9&lt;6,"",80+7*$K9/$I9)</f>
+        <v/>
+      </c>
+      <c r="V9" s="24">
+        <f>IF($N9="",$M9,$M9+$N9)</f>
         <v/>
       </c>
     </row>
@@ -8979,6 +9025,14 @@
         <f>$E10&amp;"|"&amp;$C10</f>
         <v/>
       </c>
+      <c r="U10" s="24">
+        <f>IF($G10&lt;6,"",80+7*$K10/$I10)</f>
+        <v/>
+      </c>
+      <c r="V10" s="24">
+        <f>IF($N10="",$M10,$M10+$N10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
@@ -9061,6 +9115,14 @@
         <f>$E11&amp;"|"&amp;$C11</f>
         <v/>
       </c>
+      <c r="U11" s="24">
+        <f>IF($G11&lt;6,"",80+7*$K11/$I11)</f>
+        <v/>
+      </c>
+      <c r="V11" s="24">
+        <f>IF($N11="",$M11,$M11+$N11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
@@ -9147,6 +9209,14 @@
         <f>$E12&amp;"|"&amp;$C12</f>
         <v/>
       </c>
+      <c r="U12" s="24">
+        <f>IF($G12&lt;6,"",80+7*$K12/$I12)</f>
+        <v/>
+      </c>
+      <c r="V12" s="24">
+        <f>IF($N12="",$M12,$M12+$N12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
@@ -9233,6 +9303,14 @@
         <f>$E13&amp;"|"&amp;$C13</f>
         <v/>
       </c>
+      <c r="U13" s="24">
+        <f>IF($G13&lt;6,"",80+7*$K13/$I13)</f>
+        <v/>
+      </c>
+      <c r="V13" s="24">
+        <f>IF($N13="",$M13,$M13+$N13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
@@ -9319,6 +9397,14 @@
         <f>$E14&amp;"|"&amp;$C14</f>
         <v/>
       </c>
+      <c r="U14" s="24">
+        <f>IF($G14&lt;6,"",80+7*$K14/$I14)</f>
+        <v/>
+      </c>
+      <c r="V14" s="24">
+        <f>IF($N14="",$M14,$M14+$N14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
@@ -9405,6 +9491,14 @@
         <f>$E15&amp;"|"&amp;$C15</f>
         <v/>
       </c>
+      <c r="U15" s="24">
+        <f>IF($G15&lt;6,"",80+7*$K15/$I15)</f>
+        <v/>
+      </c>
+      <c r="V15" s="24">
+        <f>IF($N15="",$M15,$M15+$N15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
@@ -9491,6 +9585,14 @@
         <f>$E16&amp;"|"&amp;$C16</f>
         <v/>
       </c>
+      <c r="U16" s="24">
+        <f>IF($G16&lt;6,"",80+7*$K16/$I16)</f>
+        <v/>
+      </c>
+      <c r="V16" s="24">
+        <f>IF($N16="",$M16,$M16+$N16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
@@ -9577,6 +9679,14 @@
         <f>$E17&amp;"|"&amp;$C17</f>
         <v/>
       </c>
+      <c r="U17" s="24">
+        <f>IF($G17&lt;6,"",80+7*$K17/$I17)</f>
+        <v/>
+      </c>
+      <c r="V17" s="24">
+        <f>IF($N17="",$M17,$M17+$N17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
@@ -9663,6 +9773,14 @@
         <f>$E18&amp;"|"&amp;$C18</f>
         <v/>
       </c>
+      <c r="U18" s="24">
+        <f>IF($G18&lt;6,"",80+7*$K18/$I18)</f>
+        <v/>
+      </c>
+      <c r="V18" s="24">
+        <f>IF($N18="",$M18,$M18+$N18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
@@ -9747,6 +9865,14 @@
       </c>
       <c r="T19" s="20">
         <f>$E19&amp;"|"&amp;$C19</f>
+        <v/>
+      </c>
+      <c r="U19" s="24">
+        <f>IF($G19&lt;6,"",80+7*$K19/$I19)</f>
+        <v/>
+      </c>
+      <c r="V19" s="24">
+        <f>IF($N19="",$M19,$M19+$N19)</f>
         <v/>
       </c>
     </row>
@@ -9831,6 +9957,14 @@
         <f>$E20&amp;"|"&amp;$C20</f>
         <v/>
       </c>
+      <c r="U20" s="24">
+        <f>IF($G20&lt;6,"",80+7*$K20/$I20)</f>
+        <v/>
+      </c>
+      <c r="V20" s="24">
+        <f>IF($N20="",$M20,$M20+$N20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
@@ -9913,6 +10047,14 @@
         <f>$E21&amp;"|"&amp;$C21</f>
         <v/>
       </c>
+      <c r="U21" s="24">
+        <f>IF($G21&lt;6,"",80+7*$K21/$I21)</f>
+        <v/>
+      </c>
+      <c r="V21" s="24">
+        <f>IF($N21="",$M21,$M21+$N21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
@@ -9995,6 +10137,14 @@
         <f>$E22&amp;"|"&amp;$C22</f>
         <v/>
       </c>
+      <c r="U22" s="24">
+        <f>IF($G22&lt;6,"",80+7*$K22/$I22)</f>
+        <v/>
+      </c>
+      <c r="V22" s="24">
+        <f>IF($N22="",$M22,$M22+$N22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
@@ -10077,6 +10227,14 @@
         <f>$E23&amp;"|"&amp;$C23</f>
         <v/>
       </c>
+      <c r="U23" s="24">
+        <f>IF($G23&lt;6,"",80+7*$K23/$I23)</f>
+        <v/>
+      </c>
+      <c r="V23" s="24">
+        <f>IF($N23="",$M23,$M23+$N23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
@@ -10159,6 +10317,14 @@
         <f>$E24&amp;"|"&amp;$C24</f>
         <v/>
       </c>
+      <c r="U24" s="24">
+        <f>IF($G24&lt;6,"",80+7*$K24/$I24)</f>
+        <v/>
+      </c>
+      <c r="V24" s="24">
+        <f>IF($N24="",$M24,$M24+$N24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
@@ -10241,6 +10407,14 @@
         <f>$E25&amp;"|"&amp;$C25</f>
         <v/>
       </c>
+      <c r="U25" s="24">
+        <f>IF($G25&lt;6,"",80+7*$K25/$I25)</f>
+        <v/>
+      </c>
+      <c r="V25" s="24">
+        <f>IF($N25="",$M25,$M25+$N25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
@@ -10323,6 +10497,14 @@
         <f>$E26&amp;"|"&amp;$C26</f>
         <v/>
       </c>
+      <c r="U26" s="24">
+        <f>IF($G26&lt;6,"",80+7*$K26/$I26)</f>
+        <v/>
+      </c>
+      <c r="V26" s="24">
+        <f>IF($N26="",$M26,$M26+$N26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
@@ -10405,6 +10587,14 @@
         <f>$E27&amp;"|"&amp;$C27</f>
         <v/>
       </c>
+      <c r="U27" s="24">
+        <f>IF($G27&lt;6,"",80+7*$K27/$I27)</f>
+        <v/>
+      </c>
+      <c r="V27" s="24">
+        <f>IF($N27="",$M27,$M27+$N27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
@@ -10487,6 +10677,14 @@
         <f>$E28&amp;"|"&amp;$C28</f>
         <v/>
       </c>
+      <c r="U28" s="24">
+        <f>IF($G28&lt;6,"",80+7*$K28/$I28)</f>
+        <v/>
+      </c>
+      <c r="V28" s="24">
+        <f>IF($N28="",$M28,$M28+$N28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
@@ -10569,6 +10767,14 @@
         <f>$E29&amp;"|"&amp;$C29</f>
         <v/>
       </c>
+      <c r="U29" s="24">
+        <f>IF($G29&lt;6,"",80+7*$K29/$I29)</f>
+        <v/>
+      </c>
+      <c r="V29" s="24">
+        <f>IF($N29="",$M29,$M29+$N29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
@@ -10651,6 +10857,14 @@
         <f>$E30&amp;"|"&amp;$C30</f>
         <v/>
       </c>
+      <c r="U30" s="24">
+        <f>IF($G30&lt;6,"",80+7*$K30/$I30)</f>
+        <v/>
+      </c>
+      <c r="V30" s="24">
+        <f>IF($N30="",$M30,$M30+$N30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
@@ -10733,6 +10947,14 @@
         <f>$E31&amp;"|"&amp;$C31</f>
         <v/>
       </c>
+      <c r="U31" s="24">
+        <f>IF($G31&lt;6,"",80+7*$K31/$I31)</f>
+        <v/>
+      </c>
+      <c r="V31" s="24">
+        <f>IF($N31="",$M31,$M31+$N31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
@@ -10815,6 +11037,14 @@
         <f>$E32&amp;"|"&amp;$C32</f>
         <v/>
       </c>
+      <c r="U32" s="24">
+        <f>IF($G32&lt;6,"",80+7*$K32/$I32)</f>
+        <v/>
+      </c>
+      <c r="V32" s="24">
+        <f>IF($N32="",$M32,$M32+$N32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="19" t="inlineStr">
@@ -10897,6 +11127,14 @@
         <f>$E33&amp;"|"&amp;$C33</f>
         <v/>
       </c>
+      <c r="U33" s="24">
+        <f>IF($G33&lt;6,"",80+7*$K33/$I33)</f>
+        <v/>
+      </c>
+      <c r="V33" s="24">
+        <f>IF($N33="",$M33,$M33+$N33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
@@ -10979,6 +11217,14 @@
         <f>$E34&amp;"|"&amp;$C34</f>
         <v/>
       </c>
+      <c r="U34" s="24">
+        <f>IF($G34&lt;6,"",80+7*$K34/$I34)</f>
+        <v/>
+      </c>
+      <c r="V34" s="24">
+        <f>IF($N34="",$M34,$M34+$N34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
@@ -11061,6 +11307,14 @@
         <f>$E35&amp;"|"&amp;$C35</f>
         <v/>
       </c>
+      <c r="U35" s="24">
+        <f>IF($G35&lt;6,"",80+7*$K35/$I35)</f>
+        <v/>
+      </c>
+      <c r="V35" s="24">
+        <f>IF($N35="",$M35,$M35+$N35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
@@ -11147,6 +11401,14 @@
         <f>$E36&amp;"|"&amp;$C36</f>
         <v/>
       </c>
+      <c r="U36" s="24">
+        <f>IF($G36&lt;6,"",80+7*$K36/$I36)</f>
+        <v/>
+      </c>
+      <c r="V36" s="24">
+        <f>IF($N36="",$M36,$M36+$N36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
@@ -11233,6 +11495,14 @@
         <f>$E37&amp;"|"&amp;$C37</f>
         <v/>
       </c>
+      <c r="U37" s="24">
+        <f>IF($G37&lt;6,"",80+7*$K37/$I37)</f>
+        <v/>
+      </c>
+      <c r="V37" s="24">
+        <f>IF($N37="",$M37,$M37+$N37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
@@ -11319,6 +11589,14 @@
         <f>$E38&amp;"|"&amp;$C38</f>
         <v/>
       </c>
+      <c r="U38" s="24">
+        <f>IF($G38&lt;6,"",80+7*$K38/$I38)</f>
+        <v/>
+      </c>
+      <c r="V38" s="24">
+        <f>IF($N38="",$M38,$M38+$N38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
@@ -11405,6 +11683,14 @@
         <f>$E39&amp;"|"&amp;$C39</f>
         <v/>
       </c>
+      <c r="U39" s="24">
+        <f>IF($G39&lt;6,"",80+7*$K39/$I39)</f>
+        <v/>
+      </c>
+      <c r="V39" s="24">
+        <f>IF($N39="",$M39,$M39+$N39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
@@ -11491,6 +11777,14 @@
         <f>$E40&amp;"|"&amp;$C40</f>
         <v/>
       </c>
+      <c r="U40" s="24">
+        <f>IF($G40&lt;6,"",80+7*$K40/$I40)</f>
+        <v/>
+      </c>
+      <c r="V40" s="24">
+        <f>IF($N40="",$M40,$M40+$N40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
@@ -11577,6 +11871,14 @@
         <f>$E41&amp;"|"&amp;$C41</f>
         <v/>
       </c>
+      <c r="U41" s="24">
+        <f>IF($G41&lt;6,"",80+7*$K41/$I41)</f>
+        <v/>
+      </c>
+      <c r="V41" s="24">
+        <f>IF($N41="",$M41,$M41+$N41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
@@ -11663,6 +11965,14 @@
         <f>$E42&amp;"|"&amp;$C42</f>
         <v/>
       </c>
+      <c r="U42" s="24">
+        <f>IF($G42&lt;6,"",80+7*$K42/$I42)</f>
+        <v/>
+      </c>
+      <c r="V42" s="24">
+        <f>IF($N42="",$M42,$M42+$N42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
@@ -11749,6 +12059,14 @@
         <f>$E43&amp;"|"&amp;$C43</f>
         <v/>
       </c>
+      <c r="U43" s="24">
+        <f>IF($G43&lt;6,"",80+7*$K43/$I43)</f>
+        <v/>
+      </c>
+      <c r="V43" s="24">
+        <f>IF($N43="",$M43,$M43+$N43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
@@ -11835,6 +12153,14 @@
         <f>$E44&amp;"|"&amp;$C44</f>
         <v/>
       </c>
+      <c r="U44" s="24">
+        <f>IF($G44&lt;6,"",80+7*$K44/$I44)</f>
+        <v/>
+      </c>
+      <c r="V44" s="24">
+        <f>IF($N44="",$M44,$M44+$N44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
@@ -11921,6 +12247,14 @@
         <f>$E45&amp;"|"&amp;$C45</f>
         <v/>
       </c>
+      <c r="U45" s="24">
+        <f>IF($G45&lt;6,"",80+7*$K45/$I45)</f>
+        <v/>
+      </c>
+      <c r="V45" s="24">
+        <f>IF($N45="",$M45,$M45+$N45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
@@ -12007,6 +12341,14 @@
         <f>$E46&amp;"|"&amp;$C46</f>
         <v/>
       </c>
+      <c r="U46" s="24">
+        <f>IF($G46&lt;6,"",80+7*$K46/$I46)</f>
+        <v/>
+      </c>
+      <c r="V46" s="24">
+        <f>IF($N46="",$M46,$M46+$N46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="19" t="inlineStr">
@@ -12093,6 +12435,14 @@
         <f>$E47&amp;"|"&amp;$C47</f>
         <v/>
       </c>
+      <c r="U47" s="24">
+        <f>IF($G47&lt;6,"",80+7*$K47/$I47)</f>
+        <v/>
+      </c>
+      <c r="V47" s="24">
+        <f>IF($N47="",$M47,$M47+$N47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
@@ -12179,6 +12529,14 @@
         <f>$E48&amp;"|"&amp;$C48</f>
         <v/>
       </c>
+      <c r="U48" s="24">
+        <f>IF($G48&lt;6,"",80+7*$K48/$I48)</f>
+        <v/>
+      </c>
+      <c r="V48" s="24">
+        <f>IF($N48="",$M48,$M48+$N48)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
@@ -12265,6 +12623,14 @@
         <f>$E49&amp;"|"&amp;$C49</f>
         <v/>
       </c>
+      <c r="U49" s="24">
+        <f>IF($G49&lt;6,"",80+7*$K49/$I49)</f>
+        <v/>
+      </c>
+      <c r="V49" s="24">
+        <f>IF($N49="",$M49,$M49+$N49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
@@ -12351,6 +12717,14 @@
         <f>$E50&amp;"|"&amp;$C50</f>
         <v/>
       </c>
+      <c r="U50" s="24">
+        <f>IF($G50&lt;6,"",80+7*$K50/$I50)</f>
+        <v/>
+      </c>
+      <c r="V50" s="24">
+        <f>IF($N50="",$M50,$M50+$N50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
@@ -12437,6 +12811,14 @@
         <f>$E51&amp;"|"&amp;$C51</f>
         <v/>
       </c>
+      <c r="U51" s="24">
+        <f>IF($G51&lt;6,"",80+7*$K51/$I51)</f>
+        <v/>
+      </c>
+      <c r="V51" s="24">
+        <f>IF($N51="",$M51,$M51+$N51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
@@ -12523,6 +12905,14 @@
         <f>$E52&amp;"|"&amp;$C52</f>
         <v/>
       </c>
+      <c r="U52" s="24">
+        <f>IF($G52&lt;6,"",80+7*$K52/$I52)</f>
+        <v/>
+      </c>
+      <c r="V52" s="24">
+        <f>IF($N52="",$M52,$M52+$N52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
@@ -12609,6 +12999,14 @@
         <f>$E53&amp;"|"&amp;$C53</f>
         <v/>
       </c>
+      <c r="U53" s="24">
+        <f>IF($G53&lt;6,"",80+7*$K53/$I53)</f>
+        <v/>
+      </c>
+      <c r="V53" s="24">
+        <f>IF($N53="",$M53,$M53+$N53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
@@ -12695,6 +13093,14 @@
         <f>$E54&amp;"|"&amp;$C54</f>
         <v/>
       </c>
+      <c r="U54" s="24">
+        <f>IF($G54&lt;6,"",80+7*$K54/$I54)</f>
+        <v/>
+      </c>
+      <c r="V54" s="24">
+        <f>IF($N54="",$M54,$M54+$N54)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
@@ -12781,6 +13187,14 @@
         <f>$E55&amp;"|"&amp;$C55</f>
         <v/>
       </c>
+      <c r="U55" s="24">
+        <f>IF($G55&lt;6,"",80+7*$K55/$I55)</f>
+        <v/>
+      </c>
+      <c r="V55" s="24">
+        <f>IF($N55="",$M55,$M55+$N55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
@@ -12867,6 +13281,14 @@
         <f>$E56&amp;"|"&amp;$C56</f>
         <v/>
       </c>
+      <c r="U56" s="24">
+        <f>IF($G56&lt;6,"",80+7*$K56/$I56)</f>
+        <v/>
+      </c>
+      <c r="V56" s="24">
+        <f>IF($N56="",$M56,$M56+$N56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
@@ -12953,6 +13375,14 @@
         <f>$E57&amp;"|"&amp;$C57</f>
         <v/>
       </c>
+      <c r="U57" s="24">
+        <f>IF($G57&lt;6,"",80+7*$K57/$I57)</f>
+        <v/>
+      </c>
+      <c r="V57" s="24">
+        <f>IF($N57="",$M57,$M57+$N57)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="19" t="inlineStr">
@@ -13039,6 +13469,14 @@
         <f>$E58&amp;"|"&amp;$C58</f>
         <v/>
       </c>
+      <c r="U58" s="24">
+        <f>IF($G58&lt;6,"",80+7*$K58/$I58)</f>
+        <v/>
+      </c>
+      <c r="V58" s="24">
+        <f>IF($N58="",$M58,$M58+$N58)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="19" t="inlineStr">
@@ -13125,6 +13563,14 @@
         <f>$E59&amp;"|"&amp;$C59</f>
         <v/>
       </c>
+      <c r="U59" s="24">
+        <f>IF($G59&lt;6,"",80+7*$K59/$I59)</f>
+        <v/>
+      </c>
+      <c r="V59" s="24">
+        <f>IF($N59="",$M59,$M59+$N59)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="19" t="inlineStr">
@@ -13211,6 +13657,14 @@
         <f>$E60&amp;"|"&amp;$C60</f>
         <v/>
       </c>
+      <c r="U60" s="24">
+        <f>IF($G60&lt;6,"",80+7*$K60/$I60)</f>
+        <v/>
+      </c>
+      <c r="V60" s="24">
+        <f>IF($N60="",$M60,$M60+$N60)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="19" t="inlineStr">
@@ -13297,6 +13751,14 @@
         <f>$E61&amp;"|"&amp;$C61</f>
         <v/>
       </c>
+      <c r="U61" s="24">
+        <f>IF($G61&lt;6,"",80+7*$K61/$I61)</f>
+        <v/>
+      </c>
+      <c r="V61" s="24">
+        <f>IF($N61="",$M61,$M61+$N61)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="19" t="inlineStr">
@@ -13383,6 +13845,14 @@
         <f>$E62&amp;"|"&amp;$C62</f>
         <v/>
       </c>
+      <c r="U62" s="24">
+        <f>IF($G62&lt;6,"",80+7*$K62/$I62)</f>
+        <v/>
+      </c>
+      <c r="V62" s="24">
+        <f>IF($N62="",$M62,$M62+$N62)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
@@ -13469,6 +13939,14 @@
         <f>$E63&amp;"|"&amp;$C63</f>
         <v/>
       </c>
+      <c r="U63" s="24">
+        <f>IF($G63&lt;6,"",80+7*$K63/$I63)</f>
+        <v/>
+      </c>
+      <c r="V63" s="24">
+        <f>IF($N63="",$M63,$M63+$N63)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
@@ -13555,6 +14033,14 @@
         <f>$E64&amp;"|"&amp;$C64</f>
         <v/>
       </c>
+      <c r="U64" s="24">
+        <f>IF($G64&lt;6,"",80+7*$K64/$I64)</f>
+        <v/>
+      </c>
+      <c r="V64" s="24">
+        <f>IF($N64="",$M64,$M64+$N64)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="19" t="inlineStr">
@@ -13641,6 +14127,14 @@
         <f>$E65&amp;"|"&amp;$C65</f>
         <v/>
       </c>
+      <c r="U65" s="24">
+        <f>IF($G65&lt;6,"",80+7*$K65/$I65)</f>
+        <v/>
+      </c>
+      <c r="V65" s="24">
+        <f>IF($N65="",$M65,$M65+$N65)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
@@ -13727,6 +14221,14 @@
         <f>$E66&amp;"|"&amp;$C66</f>
         <v/>
       </c>
+      <c r="U66" s="24">
+        <f>IF($G66&lt;6,"",80+7*$K66/$I66)</f>
+        <v/>
+      </c>
+      <c r="V66" s="24">
+        <f>IF($N66="",$M66,$M66+$N66)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
@@ -13811,6 +14313,14 @@
       </c>
       <c r="T67" s="20">
         <f>$E67&amp;"|"&amp;$C67</f>
+        <v/>
+      </c>
+      <c r="U67" s="24">
+        <f>IF($G67&lt;6,"",80+7*$K67/$I67)</f>
+        <v/>
+      </c>
+      <c r="V67" s="24">
+        <f>IF($N67="",$M67,$M67+$N67)</f>
         <v/>
       </c>
     </row>
@@ -13895,6 +14405,14 @@
         <f>$E68&amp;"|"&amp;$C68</f>
         <v/>
       </c>
+      <c r="U68" s="24">
+        <f>IF($G68&lt;6,"",80+7*$K68/$I68)</f>
+        <v/>
+      </c>
+      <c r="V68" s="24">
+        <f>IF($N68="",$M68,$M68+$N68)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
@@ -13977,6 +14495,14 @@
         <f>$E69&amp;"|"&amp;$C69</f>
         <v/>
       </c>
+      <c r="U69" s="24">
+        <f>IF($G69&lt;6,"",80+7*$K69/$I69)</f>
+        <v/>
+      </c>
+      <c r="V69" s="24">
+        <f>IF($N69="",$M69,$M69+$N69)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
@@ -14059,6 +14585,14 @@
         <f>$E70&amp;"|"&amp;$C70</f>
         <v/>
       </c>
+      <c r="U70" s="24">
+        <f>IF($G70&lt;6,"",80+7*$K70/$I70)</f>
+        <v/>
+      </c>
+      <c r="V70" s="24">
+        <f>IF($N70="",$M70,$M70+$N70)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
@@ -14145,6 +14679,14 @@
         <f>$E71&amp;"|"&amp;$C71</f>
         <v/>
       </c>
+      <c r="U71" s="24">
+        <f>IF($G71&lt;6,"",80+7*$K71/$I71)</f>
+        <v/>
+      </c>
+      <c r="V71" s="24">
+        <f>IF($N71="",$M71,$M71+$N71)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
@@ -14231,6 +14773,14 @@
         <f>$E72&amp;"|"&amp;$C72</f>
         <v/>
       </c>
+      <c r="U72" s="24">
+        <f>IF($G72&lt;6,"",80+7*$K72/$I72)</f>
+        <v/>
+      </c>
+      <c r="V72" s="24">
+        <f>IF($N72="",$M72,$M72+$N72)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
@@ -14317,6 +14867,14 @@
         <f>$E73&amp;"|"&amp;$C73</f>
         <v/>
       </c>
+      <c r="U73" s="24">
+        <f>IF($G73&lt;6,"",80+7*$K73/$I73)</f>
+        <v/>
+      </c>
+      <c r="V73" s="24">
+        <f>IF($N73="",$M73,$M73+$N73)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
@@ -14403,6 +14961,14 @@
         <f>$E74&amp;"|"&amp;$C74</f>
         <v/>
       </c>
+      <c r="U74" s="24">
+        <f>IF($G74&lt;6,"",80+7*$K74/$I74)</f>
+        <v/>
+      </c>
+      <c r="V74" s="24">
+        <f>IF($N74="",$M74,$M74+$N74)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
@@ -14489,6 +15055,14 @@
         <f>$E75&amp;"|"&amp;$C75</f>
         <v/>
       </c>
+      <c r="U75" s="24">
+        <f>IF($G75&lt;6,"",80+7*$K75/$I75)</f>
+        <v/>
+      </c>
+      <c r="V75" s="24">
+        <f>IF($N75="",$M75,$M75+$N75)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
@@ -14575,6 +15149,14 @@
         <f>$E76&amp;"|"&amp;$C76</f>
         <v/>
       </c>
+      <c r="U76" s="24">
+        <f>IF($G76&lt;6,"",80+7*$K76/$I76)</f>
+        <v/>
+      </c>
+      <c r="V76" s="24">
+        <f>IF($N76="",$M76,$M76+$N76)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
@@ -14661,6 +15243,14 @@
         <f>$E77&amp;"|"&amp;$C77</f>
         <v/>
       </c>
+      <c r="U77" s="24">
+        <f>IF($G77&lt;6,"",80+7*$K77/$I77)</f>
+        <v/>
+      </c>
+      <c r="V77" s="24">
+        <f>IF($N77="",$M77,$M77+$N77)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
@@ -14747,6 +15337,14 @@
         <f>$E78&amp;"|"&amp;$C78</f>
         <v/>
       </c>
+      <c r="U78" s="24">
+        <f>IF($G78&lt;6,"",80+7*$K78/$I78)</f>
+        <v/>
+      </c>
+      <c r="V78" s="24">
+        <f>IF($N78="",$M78,$M78+$N78)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
@@ -14831,6 +15429,14 @@
       </c>
       <c r="T79" s="20">
         <f>$E79&amp;"|"&amp;$C79</f>
+        <v/>
+      </c>
+      <c r="U79" s="24">
+        <f>IF($G79&lt;6,"",80+7*$K79/$I79)</f>
+        <v/>
+      </c>
+      <c r="V79" s="24">
+        <f>IF($N79="",$M79,$M79+$N79)</f>
         <v/>
       </c>
     </row>
@@ -20785,11 +21391,11 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>보정점수 절단(60점 미만) 발생 건수</t>
+          <t>보정점수 절단(60점 미만) 발생 건수 — ② U열 기준</t>
         </is>
       </c>
       <c r="B37" s="19">
-        <f>SUMPRODUCT(--(80+7*'평가군 계산'!$K$6:$K$79/'평가군 계산'!$I$6:$I$79&lt;60))</f>
+        <f>COUNTIF('평가군 계산'!$U$6:$U$79,"&lt;60")</f>
         <v/>
       </c>
       <c r="C37" s="19" t="n">
@@ -20803,11 +21409,11 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>보정점수 절단(100점 초과) 발생 건수</t>
+          <t>보정점수 절단(100점 초과) 발생 건수 — ② U열 기준</t>
         </is>
       </c>
       <c r="B38" s="19">
-        <f>SUMPRODUCT(--(80+7*'평가군 계산'!$K$6:$K$79/'평가군 계산'!$I$6:$I$79&gt;100))</f>
+        <f>COUNTIF('평가군 계산'!$U$6:$U$79,"&gt;100")</f>
         <v/>
       </c>
       <c r="C38" s="19" t="n">
@@ -20821,11 +21427,11 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>제7호 조정 후 절단 발생 건수</t>
+          <t>제7호 조정 후 절단 발생 건수 — ② V열 기준</t>
         </is>
       </c>
       <c r="B39" s="19">
-        <f>SUMPRODUCT(--('평가군 계산'!$M$6:$M$79+'평가군 계산'!$N$6:$N$79&lt;60))+SUMPRODUCT(--('평가군 계산'!$M$6:$M$79+'평가군 계산'!$N$6:$N$79&gt;100))</f>
+        <f>COUNTIF('평가군 계산'!$V$6:$V$79,"&lt;60")+COUNTIF('평가군 계산'!$V$6:$V$79,"&gt;100")</f>
         <v/>
       </c>
       <c r="C39" s="19" t="n">
@@ -21131,7 +21737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21146,6 +21752,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22309,6 +22916,11 @@
 (세부지침 §1-2 표기값)</t>
         </is>
       </c>
+      <c r="M47" s="34" t="inlineStr">
+        <is>
+          <t>예제 A 같은 순위와의 차</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="19" t="inlineStr">
@@ -22347,6 +22959,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G48,100),3)</f>
         <v/>
       </c>
+      <c r="M48" s="24">
+        <f>IFERROR(ROUND($H48,3)-ROUND(INDEX($H$8:$H$17,MATCH($D48,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
@@ -22385,6 +23001,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G49,100),3)</f>
         <v/>
       </c>
+      <c r="M49" s="24">
+        <f>IFERROR(ROUND($H49,3)-ROUND(INDEX($H$8:$H$17,MATCH($D49,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
@@ -22423,6 +23043,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G50,100),3)</f>
         <v/>
       </c>
+      <c r="M50" s="24">
+        <f>IFERROR(ROUND($H50,3)-ROUND(INDEX($H$8:$H$17,MATCH($D50,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
@@ -22461,6 +23085,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G51,100),3)</f>
         <v/>
       </c>
+      <c r="M51" s="24">
+        <f>IFERROR(ROUND($H51,3)-ROUND(INDEX($H$8:$H$17,MATCH($D51,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
@@ -22499,6 +23127,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G52,100),3)</f>
         <v/>
       </c>
+      <c r="M52" s="24">
+        <f>IFERROR(ROUND($H52,3)-ROUND(INDEX($H$8:$H$17,MATCH($D52,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
@@ -22537,6 +23169,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G53,100),3)</f>
         <v/>
       </c>
+      <c r="M53" s="24">
+        <f>IFERROR(ROUND($H53,3)-ROUND(INDEX($H$8:$H$17,MATCH($D53,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
@@ -22575,6 +23211,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G54,100),3)</f>
         <v/>
       </c>
+      <c r="M54" s="24">
+        <f>IFERROR(ROUND($H54,3)-ROUND(INDEX($H$8:$H$17,MATCH($D54,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
@@ -22613,6 +23253,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G55,100),3)</f>
         <v/>
       </c>
+      <c r="M55" s="24">
+        <f>IFERROR(ROUND($H55,3)-ROUND(INDEX($H$8:$H$17,MATCH($D55,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
@@ -22651,6 +23295,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G56,100),3)</f>
         <v/>
       </c>
+      <c r="M56" s="24">
+        <f>IFERROR(ROUND($H56,3)-ROUND(INDEX($H$8:$H$17,MATCH($D56,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
@@ -22689,6 +23337,10 @@
         <f>ROUND(MEDIAN(60,80+7*$G57,100),3)</f>
         <v/>
       </c>
+      <c r="M57" s="24">
+        <f>IFERROR(ROUND($H57,3)-ROUND(INDEX($H$8:$H$17,MATCH($D57,$D$8:$D$17,0)),3),"예제 A에 같은 순위가 없다")</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="34" t="inlineStr">
@@ -22757,7 +23409,16 @@
         </is>
       </c>
       <c r="B63" s="35">
-        <f>IF(SUMPRODUCT(--(ROUND($H$8:$H$17,3)&lt;&gt;ROUND($H$48:$H$57,3)))=0,"PASS — 두 예제의 보정점수가 전부 일치한다","FAIL")</f>
+        <f>IF(COUNTIF($M$48:$M$57,"&lt;&gt;0")=0,"PASS — 두 예제의 보정점수가 전부 일치한다 (차이 0)","FAIL — M열 확인")</f>
+        <v/>
+      </c>
+      <c r="H63" s="34" t="inlineStr">
+        <is>
+          <t>차이 합계</t>
+        </is>
+      </c>
+      <c r="I63" s="24">
+        <f>IFERROR(ROUND(SUM($M$48:$M$57),3),"산출 불가 — M열 확인")</f>
         <v/>
       </c>
     </row>
@@ -22783,6 +23444,9 @@
   <conditionalFormatting sqref="B63">
     <cfRule type="cellIs" priority="3" operator="containsText" dxfId="0">
       <formula>NOT(ISERROR(SEARCH("PASS",B63)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="containsText" dxfId="1">
+      <formula>NOT(ISERROR(SEARCH("FAIL",B63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
